--- a/5/search/FY2_Missile3_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY2_Missile3_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,37 +492,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>274</v>
+        <v>268.4</v>
       </c>
       <c r="B2" t="n">
-        <v>137.7</v>
+        <v>137.66</v>
       </c>
       <c r="C2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>12078.76482476344</v>
+        <v>11969.25045770651</v>
       </c>
       <c r="F2" t="n">
-        <v>273.6105282896222</v>
+        <v>299.1493725083585</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>12124.87106364936</v>
+        <v>11950.03199377308</v>
       </c>
       <c r="I2" t="n">
-        <v>-385.7394063701114</v>
+        <v>-388.8822696739174</v>
       </c>
       <c r="J2" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.800000000000001</v>
+        <v>3.700000000000003</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -530,34 +530,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>267.6</v>
+        <v>278</v>
       </c>
       <c r="B3" t="n">
-        <v>136.7</v>
+        <v>132.2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="E3" t="n">
-        <v>11955.3496654547</v>
+        <v>12169.26789231167</v>
       </c>
       <c r="F3" t="n">
-        <v>334.6752911787914</v>
+        <v>195.5963640737527</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>11925.58277575784</v>
+        <v>12252.06197007281</v>
       </c>
       <c r="I3" t="n">
-        <v>-375.541181368681</v>
+        <v>-393.5141100206074</v>
       </c>
       <c r="J3" t="n">
-        <v>1267.504</v>
+        <v>1300.775</v>
       </c>
       <c r="K3" t="n">
         <v>3.700000000000001</v>
@@ -568,37 +568,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>272.4</v>
+        <v>262</v>
       </c>
       <c r="B4" t="n">
-        <v>137.7</v>
+        <v>138.44</v>
       </c>
       <c r="C4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E4" t="n">
-        <v>12047.28347565179</v>
+        <v>11857.42328168286</v>
       </c>
       <c r="F4" t="n">
-        <v>271.8504476221754</v>
+        <v>385.5139353692858</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>12074.96160774064</v>
+        <v>11751.45409914984</v>
       </c>
       <c r="I4" t="n">
-        <v>-388.5297781599661</v>
+        <v>-368.4959775319206</v>
       </c>
       <c r="J4" t="n">
-        <v>1287.104</v>
+        <v>1251.775</v>
       </c>
       <c r="K4" t="n">
-        <v>3.699999999999999</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -606,75 +606,75 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B5" t="n">
-        <v>134.1</v>
+        <v>136.88</v>
       </c>
       <c r="C5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>11746.95453564066</v>
+        <v>12000</v>
       </c>
       <c r="F5" t="n">
-        <v>385.0900762298332</v>
+        <v>304.96</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>11558.79252368115</v>
+        <v>12000</v>
       </c>
       <c r="I5" t="n">
-        <v>-369.5865337531112</v>
+        <v>-379.4399999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1235.164</v>
+        <v>1277.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.600000000000001</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>251.2</v>
+        <v>255.2</v>
       </c>
       <c r="B6" t="n">
-        <v>132.1</v>
+        <v>135.6</v>
       </c>
       <c r="C6" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>11667.94387294839</v>
+        <v>11743.67550865691</v>
       </c>
       <c r="F6" t="n">
-        <v>424.5915353619889</v>
+        <v>429.8507389387413</v>
       </c>
       <c r="G6" t="n">
         <v>1400</v>
       </c>
       <c r="H6" t="n">
-        <v>11404.00182324069</v>
+        <v>11535.84484000035</v>
       </c>
       <c r="I6" t="n">
-        <v>-350.7331416579686</v>
+        <v>-356.7567700298467</v>
       </c>
       <c r="J6" t="n">
-        <v>1211.644</v>
+        <v>1223.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.600000000000001</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -682,75 +682,75 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>249.6</v>
+        <v>263.6</v>
       </c>
       <c r="B7" t="n">
-        <v>134.1</v>
+        <v>132.2</v>
       </c>
       <c r="C7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="E7" t="n">
-        <v>11635.40060994233</v>
+        <v>11882.11045729859</v>
       </c>
       <c r="F7" t="n">
-        <v>419.6217846312713</v>
+        <v>348.9910486957533</v>
       </c>
       <c r="G7" t="n">
         <v>1400</v>
       </c>
       <c r="H7" t="n">
-        <v>11345.59083835802</v>
+        <v>11801.06139669137</v>
       </c>
       <c r="I7" t="n">
-        <v>-359.6532070720771</v>
+        <v>-373.5776053259162</v>
       </c>
       <c r="J7" t="n">
-        <v>1211.644</v>
+        <v>1251.775</v>
       </c>
       <c r="K7" t="n">
         <v>3.600000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>266</v>
+        <v>271.6</v>
       </c>
       <c r="B8" t="n">
-        <v>137.7</v>
+        <v>136.88</v>
       </c>
       <c r="C8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>11925.07736181038</v>
+        <v>12030.57531126786</v>
       </c>
       <c r="F8" t="n">
-        <v>328.5563561779334</v>
+        <v>305.3869396262105</v>
       </c>
       <c r="G8" t="n">
         <v>1400</v>
       </c>
       <c r="H8" t="n">
-        <v>11875.12893635064</v>
+        <v>12049.68488081027</v>
       </c>
       <c r="I8" t="n">
-        <v>-385.7394063701112</v>
+        <v>-378.7462231074079</v>
       </c>
       <c r="J8" t="n">
-        <v>1267.504</v>
+        <v>1277.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.599999999999998</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -758,75 +758,75 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>251.2</v>
+        <v>262</v>
       </c>
       <c r="B9" t="n">
-        <v>106.1</v>
+        <v>132.98</v>
       </c>
       <c r="C9" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="E9" t="n">
-        <v>11610.20675099089</v>
+        <v>11851.94208827464</v>
       </c>
       <c r="F9" t="n">
-        <v>254.9898539196606</v>
+        <v>346.5132177499679</v>
       </c>
       <c r="G9" t="n">
         <v>1400</v>
       </c>
       <c r="H9" t="n">
-        <v>11398.21393135435</v>
+        <v>11750.15227396346</v>
       </c>
       <c r="I9" t="n">
-        <v>-367.7349623696468</v>
+        <v>-377.7589450469292</v>
       </c>
       <c r="J9" t="n">
-        <v>1211.644</v>
+        <v>1251.775</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>251.2</v>
+        <v>253.6</v>
       </c>
       <c r="B10" t="n">
-        <v>129.1</v>
+        <v>136.6</v>
       </c>
       <c r="C10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="D10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>11658.84308971508</v>
+        <v>11714.59796176495</v>
       </c>
       <c r="F10" t="n">
-        <v>397.8581602563216</v>
+        <v>430.2870619759283</v>
       </c>
       <c r="G10" t="n">
         <v>1400</v>
       </c>
       <c r="H10" t="n">
-        <v>11400.89518193867</v>
+        <v>11483.19090373652</v>
       </c>
       <c r="I10" t="n">
-        <v>-359.8588405254839</v>
+        <v>-355.9666715571028</v>
       </c>
       <c r="J10" t="n">
-        <v>1211.644</v>
+        <v>1223.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -834,40 +834,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>269.2</v>
+        <v>244</v>
       </c>
       <c r="B11" t="n">
-        <v>107.9</v>
+        <v>134.6</v>
       </c>
       <c r="C11" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="E11" t="n">
-        <v>11982.82568045203</v>
+        <v>11527.96194913752</v>
       </c>
       <c r="F11" t="n">
-        <v>170.0599013171152</v>
+        <v>432.1785709450572</v>
       </c>
       <c r="G11" t="n">
         <v>1400</v>
       </c>
       <c r="H11" t="n">
-        <v>11974.99178030734</v>
+        <v>11144.43103281176</v>
       </c>
       <c r="I11" t="n">
-        <v>-390.9654068540253</v>
+        <v>-354.1763401620838</v>
       </c>
       <c r="J11" t="n">
-        <v>1267.504</v>
+        <v>1192.975</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/FY2_Missile3_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY2_Missile3_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,382 +492,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>268.4</v>
+        <v>270.8</v>
       </c>
       <c r="B2" t="n">
-        <v>137.66</v>
+        <v>139</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>11969.25045770651</v>
+        <v>12015.1377959237</v>
       </c>
       <c r="F2" t="n">
-        <v>299.1493725083585</v>
+        <v>315.9056834691123</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>11950.03199377308</v>
+        <v>12024.84151125941</v>
       </c>
       <c r="I2" t="n">
-        <v>-388.8822696739174</v>
+        <v>-379.0265707173543</v>
       </c>
       <c r="J2" t="n">
         <v>1277.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.700000000000003</v>
+        <v>3.800000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>278</v>
+        <v>267.6</v>
       </c>
       <c r="B3" t="n">
-        <v>132.2</v>
+        <v>138.8</v>
       </c>
       <c r="C3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="E3" t="n">
-        <v>12169.26789231167</v>
+        <v>11955.82621039414</v>
       </c>
       <c r="F3" t="n">
-        <v>195.5963640737527</v>
+        <v>346.0453089853161</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>12252.06197007281</v>
+        <v>11925.60203855856</v>
       </c>
       <c r="I3" t="n">
-        <v>-393.5141100206074</v>
+        <v>-375.0815848668362</v>
       </c>
       <c r="J3" t="n">
-        <v>1300.775</v>
+        <v>1267.504</v>
       </c>
       <c r="K3" t="n">
-        <v>3.700000000000001</v>
+        <v>3.800000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B4" t="n">
-        <v>138.44</v>
+        <v>137.6</v>
       </c>
       <c r="C4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="E4" t="n">
-        <v>11857.42328168286</v>
+        <v>12078.70762445497</v>
       </c>
       <c r="F4" t="n">
-        <v>385.5139353692858</v>
+        <v>274.4285308108354</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>11751.45409914984</v>
+        <v>12124.78038023349</v>
       </c>
       <c r="I4" t="n">
-        <v>-368.4959775319206</v>
+        <v>-384.4425731047734</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.775</v>
+        <v>1287.104</v>
       </c>
       <c r="K4" t="n">
-        <v>3.700000000000001</v>
+        <v>3.799999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>270</v>
+        <v>251.2</v>
       </c>
       <c r="B5" t="n">
-        <v>136.88</v>
+        <v>132.2</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="E5" t="n">
-        <v>12000</v>
+        <v>11667.69250570611</v>
       </c>
       <c r="F5" t="n">
-        <v>304.96</v>
+        <v>423.8531489390987</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>12000</v>
+        <v>11403.55065126737</v>
       </c>
       <c r="I5" t="n">
-        <v>-379.4399999999999</v>
+        <v>-352.0584506221306</v>
       </c>
       <c r="J5" t="n">
-        <v>1277.5</v>
+        <v>1211.644</v>
       </c>
       <c r="K5" t="n">
-        <v>3.699999999999999</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>255.2</v>
+        <v>251.2</v>
       </c>
       <c r="B6" t="n">
-        <v>135.6</v>
+        <v>132.4</v>
       </c>
       <c r="C6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="D6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11667.18977122155</v>
+      </c>
+      <c r="F6" t="n">
+        <v>422.3763760933182</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11402.64830732073</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-354.7090685504546</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1211.644</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.700000000000001</v>
+      </c>
+      <c r="L6" t="n">
         <v>6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11743.67550865691</v>
-      </c>
-      <c r="F6" t="n">
-        <v>429.8507389387413</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1400</v>
-      </c>
-      <c r="H6" t="n">
-        <v>11535.84484000035</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-356.7567700298467</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1223.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.699999999999999</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>263.6</v>
+        <v>253.6</v>
       </c>
       <c r="B7" t="n">
-        <v>132.2</v>
+        <v>131.2</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>11882.11045729859</v>
+        <v>11703.65440689772</v>
       </c>
       <c r="F7" t="n">
-        <v>348.9910486957533</v>
+        <v>393.1040523227557</v>
       </c>
       <c r="G7" t="n">
         <v>1400</v>
       </c>
       <c r="H7" t="n">
-        <v>11801.06139669137</v>
+        <v>11481.395212071</v>
       </c>
       <c r="I7" t="n">
-        <v>-373.5776053259162</v>
+        <v>-362.0679084351775</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.775</v>
+        <v>1223.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.600000000000001</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>271.6</v>
+        <v>253.6</v>
       </c>
       <c r="B8" t="n">
-        <v>136.88</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>12030.57531126786</v>
+        <v>11707.0989726712</v>
       </c>
       <c r="F8" t="n">
-        <v>305.3869396262105</v>
+        <v>404.8076828121443</v>
       </c>
       <c r="G8" t="n">
         <v>1400</v>
       </c>
       <c r="H8" t="n">
-        <v>12049.68488081027</v>
+        <v>11481.79049011058</v>
       </c>
       <c r="I8" t="n">
-        <v>-378.7462231074079</v>
+        <v>-360.7248688708216</v>
       </c>
       <c r="J8" t="n">
-        <v>1277.5</v>
+        <v>1223.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.600000000000001</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B9" t="n">
-        <v>132.98</v>
+        <v>137.4</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="D9" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="E9" t="n">
-        <v>11851.94208827464</v>
+        <v>11925.24059195895</v>
       </c>
       <c r="F9" t="n">
-        <v>346.5132177499679</v>
+        <v>330.8906560555413</v>
       </c>
       <c r="G9" t="n">
         <v>1400</v>
       </c>
       <c r="H9" t="n">
-        <v>11750.15227396346</v>
+        <v>11875.40098659824</v>
       </c>
       <c r="I9" t="n">
-        <v>-377.7589450469292</v>
+        <v>-381.8489065740979</v>
       </c>
       <c r="J9" t="n">
-        <v>1251.775</v>
+        <v>1267.504</v>
       </c>
       <c r="K9" t="n">
-        <v>3.600000000000001</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>253.6</v>
+        <v>272.4</v>
       </c>
       <c r="B10" t="n">
-        <v>136.6</v>
+        <v>137.6</v>
       </c>
       <c r="C10" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="E10" t="n">
-        <v>11714.59796176495</v>
+        <v>12047.24913761573</v>
       </c>
       <c r="F10" t="n">
-        <v>430.2870619759283</v>
+        <v>272.6697283428562</v>
       </c>
       <c r="G10" t="n">
         <v>1400</v>
       </c>
       <c r="H10" t="n">
-        <v>11483.19090373652</v>
+        <v>12074.90716939079</v>
       </c>
       <c r="I10" t="n">
-        <v>-355.9666715571028</v>
+        <v>-387.2309184808379</v>
       </c>
       <c r="J10" t="n">
-        <v>1223.6</v>
+        <v>1287.104</v>
       </c>
       <c r="K10" t="n">
-        <v>3.600000000000001</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="B11" t="n">
-        <v>134.6</v>
+        <v>139</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="D11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>11527.96194913752</v>
+        <v>12000</v>
       </c>
       <c r="F11" t="n">
-        <v>432.1785709450572</v>
+        <v>315.8</v>
       </c>
       <c r="G11" t="n">
         <v>1400</v>
       </c>
       <c r="H11" t="n">
-        <v>11144.43103281176</v>
+        <v>12000</v>
       </c>
       <c r="I11" t="n">
-        <v>-354.1763401620838</v>
+        <v>-379.2000000000002</v>
       </c>
       <c r="J11" t="n">
-        <v>1192.975</v>
+        <v>1277.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.600000000000001</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
